--- a/InputData/ctrl-settings/GRA/Government Revenue Accounting.xlsx
+++ b/InputData/ctrl-settings/GRA/Government Revenue Accounting.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\ctrl-settings\GRA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\ctrl-settings\GRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D819826-0E41-444E-85CC-5113AD7B4B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B31A74-FEF5-46AA-8455-B6AF2D8FAC31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="698" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="698" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="GRA-carbontax" sheetId="8" r:id="rId3"/>
     <sheet name="GRA-fueltax" sheetId="9" r:id="rId4"/>
     <sheet name="GRA-evsubsidy" sheetId="10" r:id="rId5"/>
-    <sheet name="GRA-vehbatsubsidy" sheetId="18" r:id="rId6"/>
+    <sheet name="GRA-batconsubsidy" sheetId="18" r:id="rId6"/>
     <sheet name="GRA-elecgensubsidy" sheetId="11" r:id="rId7"/>
     <sheet name="GRA-eleccapconstsubsidy" sheetId="12" r:id="rId8"/>
     <sheet name="GRA-distsolarsubsidy" sheetId="13" r:id="rId9"/>
@@ -47,26 +47,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={4F81BCB5-E56D-426A-91DB-BCF0877CB817}</author>
-  </authors>
-  <commentList>
-    <comment ref="C15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    It is recommended to leave this cell set to zero and to set a non-zero value in at least one other cell in this row.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="63">
   <si>
     <t>GRA Government Revenue Accounting</t>
   </si>
@@ -249,15 +231,6 @@
   </si>
   <si>
     <t>lever.</t>
-  </si>
-  <si>
-    <t>It is recommended that you avoid using the "deficit spending" mechanism to handle "national debt</t>
-  </si>
-  <si>
-    <t>interest" to avoid creating a feedback loop where deficit spending increases debt, which increases</t>
-  </si>
-  <si>
-    <t>interest, which further increases debt, etc.</t>
   </si>
   <si>
     <t>Corporate Taxes</t>
@@ -311,7 +284,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -339,12 +312,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -381,7 +348,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -401,15 +368,13 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Jeffrey Rissman" id="{B752AA03-E7FD-47E9-A7F9-587DA10781FB}" userId="S::jeff@energyinnovation.onmicrosoft.com::f3f117cb-d7f5-455c-900f-329d977050a0" providerId="AD"/>
-</personList>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -447,7 +412,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -553,7 +518,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -695,23 +660,15 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C15" dT="2020-08-18T18:45:50.17" personId="{B752AA03-E7FD-47E9-A7F9-587DA10781FB}" id="{4F81BCB5-E56D-426A-91DB-BCF0877CB817}">
-    <text>It is recommended to leave this cell set to zero and to set a non-zero value in at least one other cell in this row.</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="80.85546875" customWidth="1"/>
@@ -732,7 +689,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -930,21 +887,6 @@
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>60</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1007,7 +949,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1072,7 +1014,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1108,7 +1050,7 @@
       </c>
       <c r="B2">
         <f t="array" ref="B2:B6">TRANSPOSE('Set Values Here'!B15:F15)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1116,7 +1058,7 @@
         <v>48</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1124,7 +1066,7 @@
         <v>49</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1137,7 +1079,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1173,7 +1115,7 @@
       </c>
       <c r="B2">
         <f t="array" ref="B2:B6">TRANSPOSE('Set Values Here'!B16:F16)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1189,7 +1131,7 @@
         <v>49</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1202,7 +1144,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1214,7 +1156,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
@@ -1272,7 +1214,7 @@
         <v>50</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1312,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1420,13 +1362,13 @@
         <v>42</v>
       </c>
       <c r="B15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C15" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1440,13 +1382,13 @@
         <v>34</v>
       </c>
       <c r="B16">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C16">
         <v>5</v>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1487,7 +1429,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1525,7 +1467,7 @@
       </c>
       <c r="C23" s="10">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D23" s="10">
         <f t="shared" si="1"/>
@@ -1537,7 +1479,7 @@
       </c>
       <c r="F23" s="10">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1671,15 +1613,15 @@
       </c>
       <c r="B29" s="10">
         <f t="shared" ref="B29:F29" si="7">IFERROR(B15/SUM($B15:$F15),1/COUNT($B15:$F15))</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C29" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" s="10">
         <f t="shared" si="7"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E29" s="10">
         <f t="shared" si="7"/>
@@ -1696,15 +1638,15 @@
       </c>
       <c r="B30" s="10">
         <f t="shared" ref="B30:F30" si="8">IFERROR(B16/SUM($B16:$F16),1/COUNT($B16:$F16))</f>
-        <v>0.33333333333333331</v>
+        <v>0</v>
       </c>
       <c r="C30" s="10">
         <f t="shared" si="8"/>
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D30" s="10">
         <f t="shared" si="8"/>
-        <v>0.33333333333333331</v>
+        <v>0</v>
       </c>
       <c r="E30" s="10">
         <f t="shared" si="8"/>
@@ -1718,7 +1660,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1776,7 +1717,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1841,10 +1782,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1906,7 +1847,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1971,7 +1912,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2036,7 +1977,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2101,7 +2042,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2166,7 +2107,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B6">
         <v>0</v>

--- a/InputData/ctrl-settings/GRA/Government Revenue Accounting.xlsx
+++ b/InputData/ctrl-settings/GRA/Government Revenue Accounting.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\ctrl-settings\GRA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Models\EPS\US\eps-us\InputData\ctrl-settings\GRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B31A74-FEF5-46AA-8455-B6AF2D8FAC31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE1C15A-F679-439B-86E7-7F30F2C1AEB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="698" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30" yWindow="0" windowWidth="19180" windowHeight="11260" tabRatio="698" firstSheet="11" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,10 @@
     <sheet name="GRA-fuelsubsidy" sheetId="14" r:id="rId10"/>
     <sheet name="GRA-CCSsubsidy" sheetId="17" r:id="rId11"/>
     <sheet name="GRA-ntnldebtinterest" sheetId="15" r:id="rId12"/>
-    <sheet name="GRA-remainder" sheetId="16" r:id="rId13"/>
+    <sheet name="GRA-indstcleanheat" sheetId="19" r:id="rId13"/>
+    <sheet name="GRA-indstprocemiss" sheetId="20" r:id="rId14"/>
+    <sheet name="GRA-hydgnprodsubs" sheetId="21" r:id="rId15"/>
+    <sheet name="GRA-remainder" sheetId="16" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="66">
   <si>
     <t>GRA Government Revenue Accounting</t>
   </si>
@@ -237,6 +240,15 @@
   </si>
   <si>
     <t>Government revenue handling is one of the design decisions a model user should make</t>
+  </si>
+  <si>
+    <t>industry clean heat subsidy</t>
+  </si>
+  <si>
+    <t>industry process emissions subsidy</t>
+  </si>
+  <si>
+    <t>hydrogen production subsidy</t>
   </si>
 </sst>
 </file>
@@ -329,7 +341,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -348,7 +360,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -365,10 +376,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1091,6 +1098,201 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7B026F0-7193-4A6C-9CD5-22217CFA3C09}">
+  <sheetPr>
+    <tabColor theme="4" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2">
+        <f t="array" ref="B2:B6">TRANSPOSE('Set Values Here'!B15:F15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2011B7B9-C3B4-4A05-B3BD-95BC1D6EBEEE}">
+  <sheetPr>
+    <tabColor theme="4" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2">
+        <f t="array" ref="B2:B6">TRANSPOSE('Set Values Here'!B15:F15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B89476C-85AD-412F-9D0D-DC84104F348D}">
+  <sheetPr>
+    <tabColor theme="4" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2">
+        <f t="array" ref="B2:B6">TRANSPOSE('Set Values Here'!B15:F15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
@@ -1364,7 +1566,7 @@
       <c r="B15">
         <v>0</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15">
         <v>5</v>
       </c>
       <c r="D15">

--- a/InputData/ctrl-settings/GRA/Government Revenue Accounting.xlsx
+++ b/InputData/ctrl-settings/GRA/Government Revenue Accounting.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Models\EPS\US\eps-us\InputData\ctrl-settings\GRA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\ctrl-settings\GRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE1C15A-F679-439B-86E7-7F30F2C1AEB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B31A74-FEF5-46AA-8455-B6AF2D8FAC31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30" yWindow="0" windowWidth="19180" windowHeight="11260" tabRatio="698" firstSheet="11" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="698" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -25,10 +25,7 @@
     <sheet name="GRA-fuelsubsidy" sheetId="14" r:id="rId10"/>
     <sheet name="GRA-CCSsubsidy" sheetId="17" r:id="rId11"/>
     <sheet name="GRA-ntnldebtinterest" sheetId="15" r:id="rId12"/>
-    <sheet name="GRA-indstcleanheat" sheetId="19" r:id="rId13"/>
-    <sheet name="GRA-indstprocemiss" sheetId="20" r:id="rId14"/>
-    <sheet name="GRA-hydgnprodsubs" sheetId="21" r:id="rId15"/>
-    <sheet name="GRA-remainder" sheetId="16" r:id="rId16"/>
+    <sheet name="GRA-remainder" sheetId="16" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="63">
   <si>
     <t>GRA Government Revenue Accounting</t>
   </si>
@@ -240,15 +237,6 @@
   </si>
   <si>
     <t>Government revenue handling is one of the design decisions a model user should make</t>
-  </si>
-  <si>
-    <t>industry clean heat subsidy</t>
-  </si>
-  <si>
-    <t>industry process emissions subsidy</t>
-  </si>
-  <si>
-    <t>hydrogen production subsidy</t>
   </si>
 </sst>
 </file>
@@ -341,7 +329,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -360,6 +348,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -376,6 +365,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1098,201 +1091,6 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7B026F0-7193-4A6C-9CD5-22217CFA3C09}">
-  <sheetPr>
-    <tabColor theme="4" tint="-0.249977111117893"/>
-  </sheetPr>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="34.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2">
-        <f t="array" ref="B2:B6">TRANSPOSE('Set Values Here'!B15:F15)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2011B7B9-C3B4-4A05-B3BD-95BC1D6EBEEE}">
-  <sheetPr>
-    <tabColor theme="4" tint="-0.249977111117893"/>
-  </sheetPr>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="34.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2">
-        <f t="array" ref="B2:B6">TRANSPOSE('Set Values Here'!B15:F15)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B89476C-85AD-412F-9D0D-DC84104F348D}">
-  <sheetPr>
-    <tabColor theme="4" tint="-0.249977111117893"/>
-  </sheetPr>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="34.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2">
-        <f t="array" ref="B2:B6">TRANSPOSE('Set Values Here'!B15:F15)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
@@ -1566,7 +1364,7 @@
       <c r="B15">
         <v>0</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="14">
         <v>5</v>
       </c>
       <c r="D15">
